--- a/inputs/templates/TEMPLATE FONDO LIQUIDEZ UNO.xlsx
+++ b/inputs/templates/TEMPLATE FONDO LIQUIDEZ UNO.xlsx
@@ -24,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
@@ -32,7 +32,8 @@
     <numFmt numFmtId="168" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="169" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="170" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="171" formatCode="[$$-1004]#,##0"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="172" formatCode="[$$-1004]#,##0"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -416,7 +417,7 @@
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="25" fillId="14" borderId="2" applyAlignment="1">
+    <xf numFmtId="172" fontId="25" fillId="14" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0"/>
@@ -460,7 +461,7 @@
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -670,6 +671,10 @@
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="28" fillId="16" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="83">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2938,7 +2943,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -2990,7 +2995,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CL"/>
           </a:p>
@@ -5546,7 +5551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK249"/>
+  <dimension ref="A1:BK251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.28515625" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" style="9" min="1" max="1"/>
@@ -6634,8 +6639,16 @@
         <f>+S11/R11-1</f>
         <v/>
       </c>
+      <c r="AI9">
+        <f>+T11/S11-1</f>
+        <v/>
+      </c>
+      <c r="AJ9">
+        <f>+U11/T11-1</f>
+        <v/>
+      </c>
       <c r="AQ9" s="29">
-        <f>+(S11/P11-1)/COUNTA(AE9:AP9)*12</f>
+        <f>+(U11/P11-1)/COUNTA(AE9:AJ9)*12</f>
         <v/>
       </c>
       <c r="AR9" s="15" t="n"/>
@@ -6736,7 +6749,14 @@
         <f>+B249</f>
         <v/>
       </c>
-      <c r="U11" s="25" t="n"/>
+      <c r="T11">
+        <f>+B250</f>
+        <v/>
+      </c>
+      <c r="U11" s="25">
+        <f>+B251</f>
+        <v/>
+      </c>
       <c r="Y11" s="25" t="n"/>
       <c r="AD11" s="32" t="inlineStr">
         <is>
@@ -7658,7 +7678,9 @@
       <c r="AR19" s="32" t="n"/>
       <c r="AS19" s="15" t="n"/>
       <c r="AV19" s="34" t="n"/>
-      <c r="AW19" s="34" t="n"/>
+      <c r="AW19" s="115" t="n">
+        <v>46203</v>
+      </c>
       <c r="AX19" s="34" t="n">
         <v>-1</v>
       </c>
@@ -7758,8 +7780,14 @@
         <f>(+S25/R25)-1</f>
         <v/>
       </c>
-      <c r="AI20" s="28" t="n"/>
-      <c r="AJ20" s="28" t="n"/>
+      <c r="AI20" s="28">
+        <f>+T25/S25-1</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="28">
+        <f>+U25/T25-1</f>
+        <v/>
+      </c>
       <c r="AK20" s="28" t="n"/>
       <c r="AL20" s="28" t="n"/>
       <c r="AM20" s="28" t="n"/>
@@ -7767,7 +7795,7 @@
       <c r="AO20" s="28" t="n"/>
       <c r="AP20" s="28" t="n"/>
       <c r="AQ20" s="29">
-        <f>+(S25/P25-1)/COUNTA(AE20:AP20)*12</f>
+        <f>+(U25/P25-1)/COUNTA(AE20:AJ20)*12</f>
         <v/>
       </c>
       <c r="AR20" s="32" t="n"/>
@@ -8307,8 +8335,14 @@
         <f>+G249</f>
         <v/>
       </c>
-      <c r="T25" s="102" t="n"/>
-      <c r="U25" s="102" t="n"/>
+      <c r="T25" s="102">
+        <f>+G250</f>
+        <v/>
+      </c>
+      <c r="U25" s="102">
+        <f>+G251</f>
+        <v/>
+      </c>
       <c r="V25" s="102" t="n"/>
       <c r="W25" s="102" t="n"/>
       <c r="X25" s="102" t="n"/>
@@ -9194,8 +9228,16 @@
         <f>+(S39/R39)-1</f>
         <v/>
       </c>
+      <c r="AI33">
+        <f>+T39/S39-1</f>
+        <v/>
+      </c>
+      <c r="AJ33">
+        <f>+U39/T39-1</f>
+        <v/>
+      </c>
       <c r="AQ33" s="29">
-        <f>+(S39/P39-1)/COUNTA(AE33:AP33)*12</f>
+        <f>+(U39/P39-1)/COUNTA(AE33:AJ33)*12</f>
         <v/>
       </c>
       <c r="AR33" s="32" t="n"/>
@@ -9732,6 +9774,14 @@
       </c>
       <c r="S39" s="9">
         <f>+K249</f>
+        <v/>
+      </c>
+      <c r="T39">
+        <f>+K250</f>
+        <v/>
+      </c>
+      <c r="U39">
+        <f>+K251</f>
         <v/>
       </c>
       <c r="AC39" s="97" t="n">
@@ -17260,6 +17310,96 @@
       </c>
       <c r="M249" s="25">
         <f>+M248*(1+L249)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="116" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B250" t="n">
+        <v>26535.18</v>
+      </c>
+      <c r="C250">
+        <f>(B250/B249-1)/(A250-A249)*30</f>
+        <v/>
+      </c>
+      <c r="D250">
+        <f>+D249*(1+C250)</f>
+        <v/>
+      </c>
+      <c r="F250" s="116" t="n">
+        <v>46173</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1432.9144</v>
+      </c>
+      <c r="H250">
+        <f>+G250+$S$148+$S$150+$S$152+$S$154+$S$156+$S$158</f>
+        <v/>
+      </c>
+      <c r="I250">
+        <f>+(H250/H249-1)/(F250-F249)*30</f>
+        <v/>
+      </c>
+      <c r="J250">
+        <f>+J249*(1+I250)</f>
+        <v/>
+      </c>
+      <c r="K250" t="n">
+        <v>6368.94</v>
+      </c>
+      <c r="L250">
+        <f>+(K250/K249-1)/(F250-F249)*30</f>
+        <v/>
+      </c>
+      <c r="M250">
+        <f>+M249*(1+L250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="116" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B251" t="n">
+        <v>26634.69</v>
+      </c>
+      <c r="C251">
+        <f>(B251/B250-1)/(A251-A250)*30</f>
+        <v/>
+      </c>
+      <c r="D251">
+        <f>+D250*(1+C251)</f>
+        <v/>
+      </c>
+      <c r="F251" s="116" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1441.5792</v>
+      </c>
+      <c r="H251">
+        <f>+G251+$S$148+$S$150+$S$152+$S$154+$S$156+$S$158</f>
+        <v/>
+      </c>
+      <c r="I251">
+        <f>+(H251/H250-1)/(F251-F250)*30</f>
+        <v/>
+      </c>
+      <c r="J251">
+        <f>+J250*(1+I251)</f>
+        <v/>
+      </c>
+      <c r="K251" t="n">
+        <v>6385.6713</v>
+      </c>
+      <c r="L251">
+        <f>+(K251/K250-1)/(F251-F250)*30</f>
+        <v/>
+      </c>
+      <c r="M251">
+        <f>+M250*(1+L251)</f>
         <v/>
       </c>
     </row>
